--- a/二叉树19/复刷记录.xlsx
+++ b/二叉树19/复刷记录.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
   <si>
     <t>题目</t>
   </si>
@@ -1368,8 +1368,12 @@
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4.24</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -1393,7 +1397,9 @@
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1418,7 +1424,9 @@
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1443,7 +1451,9 @@
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1468,7 +1478,9 @@
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1493,7 +1505,9 @@
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1518,7 +1532,9 @@
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1960,8 +1976,9 @@
       <c r="U35" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C2:C10"/>
+    <mergeCell ref="C11:C17"/>
   </mergeCells>
   <conditionalFormatting sqref="B$1:B$1048576">
     <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">

--- a/二叉树19/复刷记录.xlsx
+++ b/二叉树19/复刷记录.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
   <si>
     <t>题目</t>
   </si>
@@ -1559,8 +1559,12 @@
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4.25</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1584,7 +1588,9 @@
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -1609,7 +1615,9 @@
       <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1976,9 +1984,10 @@
       <c r="U35" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C2:C10"/>
     <mergeCell ref="C11:C17"/>
+    <mergeCell ref="C18:C20"/>
   </mergeCells>
   <conditionalFormatting sqref="B$1:B$1048576">
     <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
